--- a/public/uploads/imports/1778130407_upload_multiple_assets.xlsx
+++ b/public/uploads/imports/1778130407_upload_multiple_assets.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E0C723-787A-4474-8D93-7F94D08BCB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE81015-E6A5-4A51-8F32-102269968B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New Sheet" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Asset Name</t>
   </si>
@@ -51,6 +51,81 @@
   </si>
   <si>
     <t>PO Number</t>
+  </si>
+  <si>
+    <t>Invoice Date</t>
+  </si>
+  <si>
+    <t>Invoice No</t>
+  </si>
+  <si>
+    <t>Purchase Date</t>
+  </si>
+  <si>
+    <t>Purchase Price</t>
+  </si>
+  <si>
+    <t>Self Owned / Partner</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>Capitalization Price</t>
+  </si>
+  <si>
+    <t>End Of Life</t>
+  </si>
+  <si>
+    <t>Capitalization Date</t>
+  </si>
+  <si>
+    <t>Depreciation%</t>
+  </si>
+  <si>
+    <t>Scrap Value</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation</t>
+  </si>
+  <si>
+    <t>Income Tax Depreciation%</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Transferred To</t>
+  </si>
+  <si>
+    <t>Allotted Upto</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>AMC Vendor</t>
+  </si>
+  <si>
+    <t>Warranty Vendor</t>
+  </si>
+  <si>
+    <t>Insurance Start Date</t>
+  </si>
+  <si>
+    <t>Insurance End Date</t>
+  </si>
+  <si>
+    <t>AMC Start Date</t>
+  </si>
+  <si>
+    <t>Warranty End Date</t>
+  </si>
+  <si>
+    <t>AMC End Date</t>
+  </si>
+  <si>
+    <t>Warranty Start Date</t>
   </si>
 </sst>
 </file>
@@ -427,10 +502,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AK1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,6 +579,81 @@
       </c>
       <c r="L1" t="s">
         <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
